--- a/test/appium_tests/result/result_login.xlsx
+++ b/test/appium_tests/result/result_login.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,96 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>2025-04-20 15:27:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Failed Login</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>wrong@example.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wrongpassword</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-04-21 19:57:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Successful Login</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-04-21 19:58:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>123456</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lỗi: object of type 'int' has no len()</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-04-22 01:42:40</t>
         </is>
       </c>
     </row>

--- a/test/appium_tests/result/result_login.xlsx
+++ b/test/appium_tests/result/result_login.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,22 +451,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Failed Login</t>
+          <t>Test 7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>wrong@example.com</t>
+          <t>khai@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wrongpassword</t>
+          <t>123456</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -476,129 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-04-20 15:26:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Successful Login</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>khai@gmail.com</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2025-04-20 15:27:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Failed Login</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>wrong@example.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>wrongpassword</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2025-04-21 19:57:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Successful Login</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>khai@gmail.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2025-04-21 19:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>123456</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Lỗi: object of type 'int' has no len()</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-04-22 01:42:40</t>
+          <t>2025-04-22 02:42:05</t>
         </is>
       </c>
     </row>

--- a/test/appium_tests/result/result_login.xlsx
+++ b/test/appium_tests/result/result_login.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="18.33203125" customWidth="1" min="2" max="2"/>
+    <col width="12.88671875" customWidth="1" min="3" max="3"/>
+    <col width="33.88671875" customWidth="1" min="4" max="4"/>
+    <col width="15.6640625" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -477,6 +482,414 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>2025-04-22 02:42:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lỗi: list index out of range</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-04-22 02:55:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lỗi: list index out of range</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:02:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lỗi: list index out of range</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:02:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:04:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:05:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Test 4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>quochiep3@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:05:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Test 5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Test 6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>khai100714</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:06:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Test 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:07:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:31:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Test 4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>quochiep3@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lỗi: Message: An unknown server-side error occurred while processing the command. Original error: Timed out after 15618ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+Stacktrace:
+io.appium.uiautomator2.common.exceptions.UiAutomator2Exception: Timed out after 15618ms waiting for the root AccessibilityNodeInfo in the active window. Make sure the active window is not constantly hogging the main UI thread (e.g. the application is being idle long enough), so the accessibility manager could do its work
+	at io.appium.uiautomator2.utils.AXWindowHelpers.getActiveWindowRoot(AXWindowHelpers.java:79)
+	at io.appium.uiautomator2.utils.AXWindowHelpers.getCachedWindowRoots(AXWindowHelpers.java:117)
+	at io.appium.uiautomator2.model.internal.CustomUiDevice.findObjects(CustomUiDevice.java:148)
+	at io.appium.uiautomator2.handler.FindElements.findElements(FindElements.java:110)
+	at io.appium.uiautomator2.handler.FindElements.safeHandle(FindElements.java:75)
+	at io.appium.uiautomator2.handler.request.SafeRequestHandler.handle(SafeRequestHandler.java:59)
+	at io.appium.uiautomator2.server.AppiumServlet.handleRequest(AppiumServlet.java:266)
+	at io.appium.uiautomator2.server.AppiumServlet.handleHttpRequest(AppiumServlet.java:260)
+	at io.appium.uiautomator2.http.ServerHandler.channelRead(ServerHandler.java:68)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:366)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:352)
+	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:345)
+	at io.netty.handler.codec.MessageToMessageDecoder.channelRead(MessageToMessageDecoder.java:102)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:366)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:352)
+	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:345)
+	at io.netty.channel.CombinedChannelDuplexHandler$DelegatingChannelHandlerContext.fireChannelRead(CombinedChannelDuplexHandler.java:435)
+	at io.netty.handler.codec.ByteToMessageDecoder.fireChannelRead(ByteToMessageDecoder.java:293)
+	at io.netty.handler.codec.ByteToMessageDecoder.channelRead(ByteToMessageDecoder.java:267)
+	at io.netty.channel.CombinedChannelDuplexHandler.channelRead(CombinedChannelDuplexHandler.java:250)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:366)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:352)
+	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:345)
+	at io.netty.handler.timeout.IdleStateHandler.channelRead(IdleStateHandler.java:266)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:366)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:352)
+	at io.netty.channel.AbstractChannelHandlerContext.fireChannelRead(AbstractChannelHandlerContext.java:345)
+	at io.netty.channel.DefaultChannelPipeline$HeadContext.channelRead(DefaultChannelPipeline.java:1294)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:366)
+	at io.netty.channel.AbstractChannelHandlerContext.invokeChannelRead(AbstractChannelHandlerContext.java:352)
+	at io.netty.channel.DefaultChannelPipeline.fireChannelRead(DefaultChannelPipeline.java:911)
+	at io.netty.channel.nio.AbstractNioByteChannel$NioByteUnsafe.read(AbstractNioByteChannel.java:131)
+	at io.netty.channel.nio.NioEventLoop.processSelectedKey(NioEventLoop.java:611)
+	at io.netty.channel.nio.NioEventLoop.processSelectedKeysOptimized(NioEventLoop.java:552)
+	at io.netty.channel.nio.NioEventLoop.processSelectedKeys(NioEventLoop.java:466)
+	at io.netty.channel.nio.NioEventLoop.run(NioEventLoop.java:438)
+	at io.netty.util.concurrent.SingleThreadEventExecutor$2.run(SingleThreadEventExecutor.java:140)
+	at io.netty.util.concurrent.DefaultThreadFactory$DefaultRunnableDecorator.run(DefaultThreadFactory.java:144)
+	at java.lang.Thread.run(Thread.java:1012)
+</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:32:29</t>
         </is>
       </c>
     </row>

--- a/test/appium_tests/result/result_login.xlsx
+++ b/test/appium_tests/result/result_login.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.33203125" customWidth="1" min="2" max="2"/>
@@ -893,6 +893,414 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:05:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Test 4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>quochiep3@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:06:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Test 5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:07:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Test 6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>khai100714</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:07:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Test 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:07:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:12:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Test 4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>quochiep3@gmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:14:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Test 5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:14:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Test 6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>khai100714</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Đăng nhập không thành công: Exception: Đăng nhập không thành công</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Test 7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Đăng nhập thành công (không có thông báo lỗi)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-04-22 08:15:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
